--- a/Hasil_Penarikan_LPSE_Nasional.xlsx
+++ b/Hasil_Penarikan_LPSE_Nasional.xlsx
@@ -55,11 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +511,7378 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LPSE Nasional</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10147918000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>24 Juni 2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kementerian Perumahan dan Kawasan Permukiman</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PEMBANGUNAN RUMAH SUSUN MBR KOTA MEDAN</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Evaluasi Administrasi, Kualifikasi, Teknis, dan Harga</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>42400000000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Non Konstruksi</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/nasional/evaluasi/10147918000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LPSE Nasional</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10135726000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Tinggi, Sains, dan Teknologi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Konsultan Manajemen Konstruksi Pembangunan Gedung Rektorat ULM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>3400000000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PT. DAYA CIPTA DIANRANCANA</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>3030186003</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/nasional/evaluasi/10135726000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10084855000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>22 September 2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pembangunan Bangunan Gedung dan Kawasan Lembaga MPR dan Bangunan Pendukung di Ibu Kota Nusantara Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1700000000000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PT. HUTAMA KARYA (PERSERO)</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1701238000000</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10084855000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10084853000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>22 September 2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pembangunan Bangunan Gedung dan Kawasan Sidang Paripurna di Ibu Kota Nusantara Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1300000000000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PT. Pembangunan Perumahan (Persero) Tbk</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10084853000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10084854000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>22 September 2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pembangunan Bangunan Gedung dan Kawasan Lembaga DPD di Ibu Kota Nusantara Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1600000000000</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PT ADHI KARYA (Persero) Tbk</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10084854000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10084852000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>22 September 2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pembangunan Bangunan Gedung dan Kawasan Lembaga DPR II di Ibu Kota Nusantara Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2100000000000</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PT. WIJAYA KARYA BANGUNAN GEDUNG</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10084852000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10084842000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>22 September 2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pembangunan Bangunan Gedung dan Kawasan Lembaga Mahkamah Konstitusi, Komisi Yudisial, dan Masjid di Ibu Kota Nusantara Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1800000000000</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PT ADHI KARYA (Persero) Tbk</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10084842000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10084847000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>22 September 2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pembangunan Bangunan Gedung dan Kawasan Lembaga Mahkamah Agung dan Plaza Keadilan di Ibu Kota Nusantara Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>1400000000000</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PT. HUTAMA KARYA (PERSERO)</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10084847000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10084851000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22 September 2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pembangunan Bangunan Gedung dan Kawasan Lembaga DPR I di Ibu Kota Nusantara Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1900000000000</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PT. WASKITA KARYA (Persero) Tbk</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10084851000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10074715000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pembangunan Jaringan Perpipaan Air Minum</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>565600000000</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PT BRANTAS ABIPRAYA (Persero)</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10074715000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10067203000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Manajemen Konstruksi Bangunan/Kantor Pendukung</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>21800000000</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PT. POLA TEKNIK KONSULTAN</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>18126163470</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067203000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10067205000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Manajemen Konstruksi Induk</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>100000000000</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PT JAYA CONSTRUCTION MANAGEMENT MANGGALA PRATAMA</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>85087054384</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067205000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10071442000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pembangunan Bangunan/Kantor Pendukung</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>778200000000</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PT. Pembangunan Perumahan (Persero) Tbk</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10071442000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10069348000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pembangunan Kolam Retensi</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>355000000000</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PT. NINDYA KARYA (Persero)</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10069348000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10069347000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pembangunan Embung KIPP 1C</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>263400000000</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PT ADHI KARYA (Persero) Tbk</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10069347000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10069011000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pembangunan Embung KIPP 1B</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>331600000000</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PT, BUMI KARSA</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10069011000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10067210000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Supervisi Pembangunan Jalan Kawasan Kompleks Yudikatif</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>21800000000</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PT. PERENTJANA DJAJA</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>17956217919</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067210000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10067212000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Supervisi Pembangunan Embung KIPP 1B</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>17500000000</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>PT. RAYAKONSULT</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>14508366000</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067212000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10067208000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Supervisi Pembangunan Jalan Kawasan Kompleks Legislatif</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>19900000000</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PT. Agrinas Jaladri Nusantara (Persero)</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>16585145808</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067208000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10067213000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Supervisi Pembangunan Embung KIPP 1C</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>14500000000</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PT. Mitra Utama Kenzo</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>11898223200</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067213000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10067211000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Supervisi Pembangunan Jalan Kawasan Pendukung</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>21100000000</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PT Formasi Empat Pola Selaras Konsultan</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>17878344204</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067211000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10067214000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Supervisi Pembangunan Kolam Retensi</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>18000000000</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>PT. RAYAKONSULT</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>14392876050</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067214000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10067216000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Supervisi Pembangunan Jaringan Perpipaan Air Minum</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>34400000000</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PT. Mitra Utama Kenzo</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>27641622898</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067216000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10068149000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pembangunan Jalan Kawasan Pendukung KIPP 1A</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1200000000000</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>PT. Jaya Konstruksi Manggala Pratama, Tbk</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>1145275834721</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10068149000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10067201000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Manajemen Konstruksi Pembangunan Gedung dan Kawasan Lembaga DPD dan MPR Termasuk Bangunan Pendukung di Ibu Kota Nusantara</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>54900000000</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PT JAYA CONSTRUCTION MANAGEMENT MANGGALA PRATAMA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>48283710735</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067201000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10067185000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Manajemen Konstruksi Pembangunan Gedung dan Kawasan Lembaga DPR I dan Paripurna</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>54900000000</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>PT. Ciriajasa Cipta Mandiri</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>44010752415</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067185000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kementerian PUPR</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10067202000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (OIKN)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Manajemen Konstruksi Pembangunan Gedung dan Kawasan Kompleks Yudikatif di Ibu Kota Nusantara</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PT. CIRIAJASA ENGINEERING CONSULTANS</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>40770973215</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pu/evaluasi/10067202000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10156265000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>22 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PDAM Tirta Mahakam</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEMBANGUNAN KANTOR PERUMDA TIRTA MAHAKAM KABUPATEN KUTAI KARTANEGARA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Evaluasi Administrasi, Kualifikasi, Teknis, dan Harga</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>19300000000</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10156265000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10143563000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10 Juni 2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PDAM Tirta Mahakam</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PENGAWASAN TEKNIS PEMBANGUNAN KANTOR PERUMDA TIRTA MAHAKAM KAB. KUKAR</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>13. Pembukaan dan Evaluasi Penawaran File I: Administrasi dan Teknis</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>649900000000000</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10143563000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10137060000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lembaga Kebijakan Pengadaan Barang/Jasa Pemerintah</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Pembangunan dan Pengembangan Platform Layanan LKPP Terintegrasi Tahun 2026 Seleksi Ulang</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>189300000000000</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>PT. Javan Cipta Solusi</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>187590000</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10137060000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10136485000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>15 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lembaga Kebijakan Pengadaan Barang/Jasa Pemerintah</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Pengadaan Jasa Konsultansi Badan Usaha Penyusunan Kajian Proses Pengadaan untuk Program Makan Bagi Siswa Sekolah Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>343200000000000</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10136485000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10130409000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>22 April 2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lembaga Kebijakan Pengadaan Barang/Jasa Pemerintah</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Jasa Konsultan Software Developer Layanan  Pengembangan Strategi dan Kebijakan Pengadaan Tahun 2026 Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>100800000000000</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ILYAS YASIN</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>98000000</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10130409000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10128436000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>15 April 2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lembaga Kebijakan Pengadaan Barang/Jasa Pemerintah</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Jasa Konsultan Senior Software Developer Sistem Layanan Hukum dan Penyelesaian Sanggah</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>123200000000000</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Alex Putra Setiadi</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>120400000</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10128436000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10126147000</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7 April 2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Lembaga Kebijakan Pengadaan Barang/Jasa Pemerintah</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Jasa Konsultan Software Developer Layanan  Pengembangan Strategi dan Kebijakan Pengadaan Tahun 2026 Tender Gagal</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tender Gagal</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>110300000000000</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10126147000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10123552000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>26 Maret 2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lembaga Kebijakan Pengadaan Barang/Jasa Pemerintah</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Pengembangan Layanan Sistem Audit dan Monitoring Tahun 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>164500000000000</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Adhyamitra Tata Sarana</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>131035500</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10123552000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10122098000</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>12 Maret 2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Lembaga Kebijakan Pengadaan Barang/Jasa Pemerintah</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Pembangunan dan Pengembangan Platform Layanan LKPP Terintegrasi Tahun 2026 Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>265000000000000</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10122098000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10111883000</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>26 Januari 2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Kementerian Koordinator Bidang Perekonomian</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Badan Usaha Pendukung Project Management Office (PMO) dalam Proyek Strategis Nasional (PSN) dan Kebijakan Percepatan Infrastruktur</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>PT. PROSPERA CONSULTING ENGINEERS</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>3805328085</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/10111883000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LKPP Pusat</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>9944119</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>26 Januari 2024</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Kementerian Perencanaan Pembangunan Nasional</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JASA KONSULTANSI KONSTRUKSI PENGAWASAN PEKERJAAN PEMBANGUNAN PAVILIUN INDONESIA PADA EXPO 2025 DI OSAKA, JEPANG</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>23000000000</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>PT. DETA DECON</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>22120344299</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/lkpp/evaluasi/9944119/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10071672000</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>13 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Pengadaan Jasa Konsultansi Pengawas Pengadaan Kapal Patroli FPB 28 Tahun Anggaran 2025, 2026 dan 2027 Seleksi Ulang</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>3200000000</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>PT. ZATRIA AWAN CONSULTANT</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>3048603597</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemenkeu/evaluasi/10071672000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10071654000</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>13 Agustus 2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pengadaan Jasa Konsultansi Pengawas Pengadaan Kapal Patroli FPB 38 Tahun Anggaran 2025, 2026, dan 2027 Seleksi Ulang</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>PT. ZATRIA AWAN CONSULTANT</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>3785439390</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemenkeu/evaluasi/10071654000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10059392000</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>15 Juli 2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pengadaan Jasa Konsultansi Pengawas Pengadaan Kapal Patroli FPB 38 Tahun Anggaran 2025, 2026, dan 2027 Seleksi Ulang Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemenkeu/evaluasi/10059392000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10060145000</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>16 Juli 2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pengadaan Jasa Konsultansi Pengawas Pengadaan Kapal Patroli FPB 28 Tahun Anggaran 2025, 2026 dan 2027 Seleksi Ulang Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemenkeu/evaluasi/10060145000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10014907000</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>18 Februari 2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pengadaan Jasa Konsultansi Pengawas Pengadaan Kapal Patroli FPB 38 Tahun Anggaran 2025, 2026, dan 2027 Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemenkeu/evaluasi/10014907000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10015895000</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>25 Februari 2025</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Pengadaan Jasa Konsultansi Pengawas Pengadaan Kapal Patroli FPB 28 Tahun Anggaran 2025, 2026 dan 2027 Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemenkeu/evaluasi/10015895000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>40135011</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>26 Agustus 2024</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PENGADAAN JASA KONSULTANSI MANAJEMEN KONSTRUKSI PEMBANGUNAN RUMAH SUSUN NEGARA KEMENTERIAN KEUANGAN DI BALIKPAPAN (KONTRAK TAHUN JAMAK TAHUN ANGGARAN 2024 S.D 2027)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>11800000000</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>PT. BIRO ARSITEK DAN INSINJUR SANGKURIANG</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>11449902603</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemenkeu/evaluasi/40135011/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>40118011</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>16 Agustus 2024</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PENGADAAN JASA KONSULTANSI MANAJEMEN KONSTRUKSI PEMBANGUNAN RUMAH SUSUN NEGARA KEMENTERIAN KEUANGAN DI BALIKPAPAN (KONTRAK TAHUN JAMAK TAHUN ANGGARAN 2024 S.D 2027) Seleksi Batal</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Seleksi Batal</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>11800000000</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemenkeu/evaluasi/40118011/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>40117011</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16 Agustus 2024</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PENGADAAN JASA KONSULTANSI PERENCANAAN KONSTRUKSI PEMBANGUNAN RUMAH SUSUN NEGARA KEMENTERIAN KEUANGAN DI BALIKPAPAN (KONTRAK TAHUN JAMAK TAHUN ANGGARAN 2024 S.D 2027)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>12900000000</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>PT. PENTA REKAYASA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>12499876930</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemenkeu/evaluasi/40117011/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10150196000</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Pembangunan Gardu Traksi Delanggu (MYC 2026 - 2027) Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>10. Download Dokumen Pemilihan</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>55300000000</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10150196000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10135545000</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>12 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Pembangunan Gardu Traksi Delanggu (MYC 2026 - 2027) Tender Gagal</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tender Gagal</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>55300000000</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10135545000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10115733000</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>12 Februari 2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Rehabilitasi Fasilitas Pelabuhan Kolaka MYC TA. 2026 - 2027 (Tender Tidak Mengikat)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>71000000000</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>PT. SULAWESI MAKMUR PRATAMA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>64134423171</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10115733000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10119224000</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2 Maret 2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Rehabilitasi Fasilitas Pelabuhan Laut Bunta MYC 2026 - 2027 (Lelang Tidak Mengikat) Tender Ulang</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>68099999999.99999</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>PT. SULAWESI MAKMUR PRATAMA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>61359304242</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10119224000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>10111958000</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>26 Januari 2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Replacement Fasilitas Pelabuhan Laut Boepinang (MYC 2026-2027)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>81300000000</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>PT. KARYA PEMBANGUNAN REZKI</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>77060707747</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10111958000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>10099097000</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>17 November 2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Rehabilitasi Fasilitas Pelabuhan Laut Bunta MYC 2026 - 2027 (Lelang Tidak Mengikat) Tender Gagal</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tender Gagal</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>68099999999.99999</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10099097000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>10103634000</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>12 Desember 2025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Replacement Fasilitas Pelabuhan Larea-Rea Sinjai (MYC 2026-2027) Tender Tidak Mengikat</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>89900000000</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>PT. SULAWESI MAKMUR PRATAMA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>82709375507</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10103634000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10110077000</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>15 Januari 2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Replacement Fasilitas Pelabuhan Salura (MYC 2026-2027)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>96600000000</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>PT. Karya Dwiputra Indonesia</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>92051860000</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10110077000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>10108139000</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3 Januari 2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>REPLACEMENT FASILITAS PELABUHAN LAUT SAILUS MYC TA. 2026-2027</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>73000000000</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>PT. KARYA PEMBANGUNAN REZKI</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>69913382704</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10108139000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10108707000</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>7 Januari 2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Pengembangan Fasilitas Pelabuhan Laut Sungai Nyamuk TA.2026-2027</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>72400000000</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>PT. SENA SANJAYA MAKMUR SEJAHTERA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>66490499800</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10108707000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>10105221000</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>19 Desember 2025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Replacement Fasilitas Pelabuhan Laut Tahuna ( MYC 2026 - 2027) (Lelang Tidak Mengikat)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>96500000000</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>PT. Pilar Dasar Membangun</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>89715298023</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10105221000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>10061246000</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>18 Juli 2025</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Konsultan Manajemen Konstruksi Pembangunan Fasilitas Sisi Darat Bandar Udara VVIP IKN Tahap II (Seleksi Tidak Mengikat) Seleksi Batal</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Seleksi Batal</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>9000000000</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10061246000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Kementerian Perhub</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>10061316000</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>18 Juli 2025</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Pembangunan Fasilitas Sisi Darat Bandar Udara VVIP IKN Tahap II (Tender Tidak Mengikat) Tender Batal</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tender Batal</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>186800000000</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/dephub/evaluasi/10061316000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>10149268000</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>29 Juni 2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Konstruksi Fisik - Pelaksanaan Pembangunan/Renovasi Kab. Nias Selatan (RSU Kelas D Pratama Kab. Nias Selatan)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>10. Download Dokumen Pemilihan</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>123200000000</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemkes/evaluasi/10149268000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10147639000</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>23 Juni 2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Belanja Langganan Daya dan Jasa : Belanja Penyediaan Barang dan Jasa BLU Lainnya - Jasa Konsultan Penyusunan DED/Blueprint SIMRS Terintegrasi dan Implementasi Sistem Smart Hospital,Pengembangan dan Implementasi Enterprice Resource Planning (ERP) Smart Hospital pada RS Jantung dan Pembuluh Darah Harapan Kita</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>13. Pembukaan dan Evaluasi Penawaran File I: Administrasi dan Teknis</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>5600000000</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Terintegrasi</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemkes/evaluasi/10147639000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:34:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>10154774000</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>17 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Pembangunan Prasarana Sapi Perah Terintegrasi</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Evaluasi Administrasi, Kualifikasi, Teknis, dan Harga</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>69700000000</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pertanian/evaluasi/10154774000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>10133582000</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>5 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Pembangunan Gedung Laboratorium Penyakit Hewan Menular, Penyakit Infeksi Baru (PHM-PIB) dan Zoonosis untuk Kesehatan Semua</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>67400000000.00001</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>PT. RAZASA KARYA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>55950909220</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pertanian/evaluasi/10133582000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>10129771000</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>21 April 2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Rehabilitasi Ruang Seminar 1 dan Ruang Seminar Kecil</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>808600000000000</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>CV. KARYA HERDIANSYAH</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pertanian/evaluasi/10129771000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>10130666000</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>23 April 2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Pembangunan Gedung Laboratorium Penyakit Hewan Menular, Penyakit Infeksi Baru (PHM-PIB) dan Zoonosis untuk Kesehatan Semua Tender Batal</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tender Batal</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>67400000000.00001</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pertanian/evaluasi/10130666000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>10125733000</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>6 April 2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Project Management Office (PMO) Kegiatan Cetak Sawah</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>PT.Caturbina Guna Persada</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>3306330382</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pertanian/evaluasi/10125733000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>10124170000</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>30 Maret 2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Rehab Kandang Tender Batal</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tender Batal</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>845500000000000</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pertanian/evaluasi/10124170000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10116590000</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>18 Februari 2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Biaya Konstruksi Fisik</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>63400000000</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>PT. PANDAWA LAND NUSANTARA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>57393300000</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pertanian/evaluasi/10116590000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10116341000</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>17 Februari 2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Pembangunan/Renovasi gedung dan bangunan balai pelatihan pertanian Tender Batal</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tender Batal</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>611800000000000</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>cv.duta persada indoguna</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pertanian/evaluasi/10116341000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2510212</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>31 Agustus 2015</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan, Kementerian Pertanian</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Pengadaan Partisi Kantor Pusat</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>745400000000000</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>KARISMA CITRA BAHARI</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/pertanian/evaluasi/2510212/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>10157094000</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>25 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Kementerian Energi Dan Sumber Daya Mineral</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>KONSULTAN PENGAWAS PEMBANGUNAN JARINGAN GAS BUMI UNTUK RUMAH TANGGA KOTA DEPOK, KABUPATEN JOMBANG, KABUPATEN LAMONGAN, KABUPATEN PASURUAN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2. Download Dokumen Kualifikasi</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>206900000000</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/esdm/evaluasi/10157094000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>10157118000</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>26 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Kementerian Energi Dan Sumber Daya Mineral</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>KONSULTAN PENGAWAS PEMBANGUNAN JARINGAN GAS BUMI UNTUK RUMAH TANGGA KABUPATEN BOGOR, KABUPATEN TANGERANG, KABUPATEN BEKASI, KABUPATEN CIREBON</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2. Download Dokumen Kualifikasi</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>238300000000</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/esdm/evaluasi/10157118000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>10157134000</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>26 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Kementerian Energi Dan Sumber Daya Mineral</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PEMBANGUNAN JARINGAN GAS BUMI UNTUK RUMAH TANGGA KABUPATEN BOGOR, KABUPATEN TANGERANG, KABUPATEN BEKASI, KABUPATEN CIREBON</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2. Download Dokumen Kualifikasi</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>4400000000000</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/esdm/evaluasi/10157134000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>10157095000</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>25 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Kementerian Energi Dan Sumber Daya Mineral</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PEMBANGUNAN JARINGAN GAS BUMI UNTUK RUMAH TANGGA KOTA DEPOK, KABUPATEN JOMBANG, KABUPATEN LAMONGAN, KABUPATEN PASURUAN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2. Download Dokumen Kualifikasi</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>3800000000000</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/esdm/evaluasi/10157095000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>10134857000</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>9 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Kementerian Energi Dan Sumber Daya Mineral</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Manajemen Konstruksi Pembangunan Gedung PEP Bandung</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>19. Surat Penunjukan Penyedia Barang/Jasa</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>7400000000</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>PT. CIRIAJASA ENGINEERING CONSULTANS</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>6398361900</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/esdm/evaluasi/10134857000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Kementerian Pertahanan</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>10131802000</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>28 April 2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Kementerian Pertahanan</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Renovasi Ruang Gedung DI Pandjaitan Ditjen Kuathan Kemhan TA. 2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>8100000000</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>PT. WIJAYA PUTRA PERKASA SELARAS</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>8060500318</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemhan/evaluasi/10131802000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>10159044000</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Konsultan Pengawas Pengawasan Konstruksi Renovasi Gedung Data Center di IPDN Cilandak</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1. Pengumuman Prakualifikasi</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>567900000000000</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10159044000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>10157794000</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>28 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Evaluasi dan Penyusunan Peta Proses Bisnis Kemendagri Seleksi Ulang</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1. Pengumuman Prakualifikasi</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>181900000000000</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10157794000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>10157270000</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>27 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Pengembangan SIETIK</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2. Download Dokumen Kualifikasi</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>503200000000000</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10157270000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>10152869000</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>10 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Pembangunan Rumah Singgah/Jagat Bali di IPDN Kampus Jatinangor Tahun 2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Evaluasi Administrasi, Kualifikasi, Teknis, dan Harga</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>16000000000</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10152869000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>10152323000</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>8 Juli 2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Penyempurnaan Modul Informasi Pembangunan daerah dalam SIPD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>10. Download Dokumen Pemilihan</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>500000000000000</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10152323000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>10145444000</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>17 Juni 2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Pengembangan Website Setjen Berbasis Microservices</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>19. Surat Penunjukan Penyedia Barang/Jasa</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>473900000000000</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Karya Berdiri Bersama</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>433532700</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10145444000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>10144361000</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>12 Juni 2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Evaluasi dan Penyusunan Peta Proses Bisnis Kemendagri Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>181900000000000</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10144361000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>10143349000</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>9 Juni 2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Pengawasan Kontruksi Renovasi Gedung Angso Duo Seleksi Ulang</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>199400000000000</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>PT Delta Arsitektur Persada</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>177872893</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10143349000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>10139182000</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>25 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Penguatan Sistem Pengendalian Intern Pemerintah (SPIP) dan Survei Penilaian Integritas (SPI) lingkup Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>779400000000000</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>PT ALCHEMIST LAW OFFICE</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>731723100</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10139182000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10139426000</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>25 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Pekerjaan Pengawasan Konstruksi Pembangunan Balai Pelatihan Kompetensi Fungsional Aparatur Pemerintahan Dalam Negeri Bidang Administrasi Kewilayahan Ditjen Bina Administrasi Kewilayahan Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>888000000000000</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>PT. PUTRA ANDESPAL PERKASA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>843431280</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10139426000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>10138637000</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>22 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Pengembangan Portal Satu Data Pemerintahan Dalam Negeri (PELITA)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>499900000000000</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>PT. Waditra Reka Cipta</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>476556300</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10138637000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>10136937000</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>18 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Pengawasan Kontruksi Renovasi Gedung Angso Duo Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Seleksi Gagal</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>199400000000000</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10136937000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>10136616000</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>17 Mei 2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Pekerjaan Konstruksi Rehabilitasi Gedung Asthabrata Balai Besar Pengembangan Kompetensi Aparatur Pemerintahan Dalam Negeri III (BBPKA-PDN III)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>5200000000</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>CV. AKRE INDONESIA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>4801857000</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10136616000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>10132089000</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>29 April 2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Pengembangan Aplikasi SIAK Terpusat Seleksi Batal</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Seleksi Batal</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>3100000000</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Belum Ditetapkan</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10132089000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>10128386000</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>15 April 2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Dukungan Manajemen Pemenuhan Layanan Dasar</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>949900000000000</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>PT. Phibetha Kalamwijaya</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>854692674</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10128386000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>10128304000</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>14 April 2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Pembangunan Konsolidator Data Administrasi Kewilayahan</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>PT. LAWU ALAM</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>2454903750</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10128304000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>10128644000</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>15 April 2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Biaya Jasa Konsultan Pengawas Konstruksi Renovasi Gedung Kantor di Sukajadi</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>399900000000000</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>PT.BINA MUDA KONSULTAN</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10128644000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>10126392000</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>8 April 2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Konsultan Pengawas Renovasi Perluasan Gedung Arsip I Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>280600000000000</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>PT. HUDA TATA SARANA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>201814650</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10126392000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>10128425000</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>15 April 2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Pemutakhiran E-Monev Ditjen Bina Adwil</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>999900000000000</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>PT PUTRA BESAR ABADI</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>980485200</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10128425000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>10128292000</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>14 April 2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Pengelolaan Penyajian Data Ke Dalam Dashboard Monitoring Bidang Administrasi Kewilayahan</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tender Sudah Selesai</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>1000000000000000</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Seleksi / Tender</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Prakualifikasi / Pascakualifikasi</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Kualitas &amp; Biaya</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Jasa Konsultansi Badan Usaha Konstruksi</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>PT. HEXSA INDOTECH CONSULTANTS</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>980407500</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>https://spse.inaproc.id/kemendagri/evaluasi/10128292000/pemenangberkontrak</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2026-08-05 14:35:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
